--- a/222222222222222.xlsx
+++ b/222222222222222.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9096"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,106 +24,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
-  <si>
-    <t>IDSP</t>
-  </si>
-  <si>
-    <t>Mã sp</t>
-  </si>
-  <si>
-    <t>Link sp</t>
-  </si>
-  <si>
-    <t>Tên shop</t>
-  </si>
-  <si>
-    <t>Linh otkey</t>
-  </si>
-  <si>
-    <t>Từ khóa/ Nhóm</t>
-  </si>
-  <si>
-    <t>Link ảnh</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+  <si>
+    <t>A823438090641</t>
+  </si>
+  <si>
+    <t>https://detail.1688.com/offer/823438090641.html</t>
+  </si>
+  <si>
+    <t>石狮市布梵衣阁服饰有限公司</t>
+  </si>
+  <si>
+    <t>厚底老爹鞋女款2026春季新款水钻时尚内增高女鞋百搭运动休闲鞋子</t>
+  </si>
+  <si>
+    <t>A895582595373</t>
+  </si>
+  <si>
+    <t>https://detail.1688.com/offer/895582595373.html</t>
+  </si>
+  <si>
+    <t>老爹鞋女2026秋冬新款加绒网面鞋休闲运动鞋子百搭厚底内增高女鞋</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>chinese_name</t>
+  </si>
+  <si>
+    <t>shop_name_chinese</t>
   </si>
   <si>
     <t>Tên tiếng trung</t>
   </si>
   <si>
-    <t>Shop name</t>
-  </si>
-  <si>
-    <t>Shop id</t>
-  </si>
-  <si>
-    <t>Giá thấp hơn</t>
-  </si>
-  <si>
-    <t>Giá cao hơn</t>
-  </si>
-  <si>
-    <t>Hệ số giá</t>
-  </si>
-  <si>
-    <t>Hạng giá</t>
-  </si>
-  <si>
-    <t>A945288196352</t>
-  </si>
-  <si>
-    <t>https://detail.1688.com/offer/945288196352.html</t>
-  </si>
-  <si>
-    <t>石狮市布梵衣阁服饰有限公司</t>
-  </si>
-  <si>
-    <t>Shishi Bufan Clothing Co Ltd</t>
-  </si>
-  <si>
-    <t>giày dép nữ</t>
-  </si>
-  <si>
-    <t>giày dép sandal nữ</t>
-  </si>
-  <si>
-    <t>https://188.com.vn/uploads/size-san-pham/size%20gi%C3%A0y%20n%E1%BB%AF.jpg</t>
-  </si>
-  <si>
-    <t>厚底凉鞋女小个子增高8CM2026夏季新款时尚外穿百搭透气凉靴女鞋</t>
-  </si>
-  <si>
-    <t>giày dép sandal nữ shtdcl</t>
-  </si>
-  <si>
-    <t>giày dép sandal nữ G03</t>
-  </si>
-  <si>
-    <t>giày dép sandal nữ G05</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>G04</t>
-  </si>
-  <si>
-    <t>Giá tệ</t>
-  </si>
-  <si>
-    <t>Giá vnd</t>
-  </si>
-  <si>
-    <t>A0000</t>
-  </si>
-  <si>
-    <t>https://hibox.mn/v/abb-1032041905142</t>
+    <t>Shop Trung Quốc</t>
+  </si>
+  <si>
+    <t>Giá Tệ</t>
+  </si>
+  <si>
+    <t>China price</t>
+  </si>
+  <si>
+    <t>ID SP</t>
+  </si>
+  <si>
+    <t>Link SP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,12 +90,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,7 +117,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -156,17 +125,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -445,122 +431,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="12.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="12.88671875" style="2"/>
+    <col min="6" max="6" width="59.77734375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="12.88671875" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E3" s="2">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="B4" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>110</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <v>109</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2">
-        <v>1130000</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/222222222222222.xlsx
+++ b/222222222222222.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>A823438090641</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Link SP</t>
+  </si>
+  <si>
+    <t>Sku</t>
   </si>
 </sst>
 </file>
@@ -439,10 +442,13 @@
     <col min="7" max="16384" width="12.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
@@ -456,10 +462,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -473,7 +482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -493,7 +502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
